--- a/data/trans_camb/P1401-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1401-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,85</t>
+          <t>-0,24; 2,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,61</t>
+          <t>1,74; 4,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,19</t>
+          <t>-1,16; 3,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,78</t>
+          <t>-1,55; 1,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,1</t>
+          <t>-0,14; 2,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,84</t>
+          <t>0,84; 3,0</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1168,77%</t>
+          <t>1210,59%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>218,93%</t>
+          <t>230,33%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,35; 499,11</t>
+          <t>-53,39; 485,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,61; 288,1</t>
+          <t>-56,94; 294,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 627,91</t>
+          <t>-28,28; 504,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,24; 847,1</t>
+          <t>41,87; 916,36</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,82</t>
+          <t>-1,58; 0,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,82</t>
+          <t>-0,19; 2,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,11</t>
+          <t>-3,02; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,72</t>
+          <t>-2,16; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,64</t>
+          <t>-1,73; 0,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,82</t>
+          <t>-0,56; 1,81</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>119,43%</t>
+          <t>129,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 798,38</t>
+          <t>-21,16; 915,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 273,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 276,83</t>
+          <t>-68,39; 243,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,67; 124,66</t>
+          <t>-86,7; 115,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 266,25</t>
+          <t>-28,97; 245,97</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,54</t>
+          <t>-3,01; 0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,3</t>
+          <t>-1,47; 2,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,22</t>
+          <t>-1,92; 6,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,8</t>
+          <t>-4,67; 0,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,14</t>
+          <t>-2,07; 1,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,9</t>
+          <t>-1,85; 1,4</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-22,89%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-47,29%</t>
+          <t>-50,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-31,48%</t>
+          <t>-8,35%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-83,17; 78,1</t>
+          <t>-82,55; 73,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 74,61</t>
+          <t>-46,66; 158,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 358,6</t>
+          <t>-54,59; 364,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,49; 57,57</t>
+          <t>-89,2; 44,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,92; 73,8</t>
+          <t>-62,39; 56,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,45; 45,49</t>
+          <t>-51,93; 85,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,17</t>
+          <t>-1,59; 0,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,67</t>
+          <t>-0,47; 1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,7</t>
+          <t>-1,44; 1,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,79</t>
+          <t>-1,83; 1,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,52</t>
+          <t>-1,1; 0,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,99</t>
+          <t>-0,44; 1,18</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-22,38%</t>
+          <t>-3,07%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 33,6</t>
+          <t>-81,91; 25,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 184,72</t>
+          <t>-30,83; 196,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 152,79</t>
+          <t>-51,45; 161,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 68,36</t>
+          <t>-53,65; 114,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,72; 51,11</t>
+          <t>-53,9; 50,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 89,37</t>
+          <t>-22,99; 113,48</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,8</t>
+          <t>-0,48; 1,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,01</t>
+          <t>-0,48; 1,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,01</t>
+          <t>-1,35; 2,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,99</t>
+          <t>-0,79; 2,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,45</t>
+          <t>-0,77; 1,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,6</t>
+          <t>-0,38; 1,66</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,05; 658,11</t>
+          <t>-50,79; 721,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 777,32</t>
+          <t>-48,05; 761,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-44,61; 128,12</t>
+          <t>-42,77; 147,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 120,37</t>
+          <t>-25,78; 130,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 120,65</t>
+          <t>-33,77; 129,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 128,37</t>
+          <t>-16,55; 139,84</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,0</t>
+          <t>-1,95; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,0</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,44</t>
+          <t>-1,57; 0,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,82</t>
+          <t>-0,45; 1,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,32</t>
+          <t>-1,45; 0,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,22</t>
+          <t>-0,6; 1,23</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,45; 42,39</t>
+          <t>-69,4; 40,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 152,7</t>
+          <t>-23,16; 145,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-71,04; 33,91</t>
+          <t>-73,53; 36,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 121,03</t>
+          <t>-33,91; 121,36</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,57</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,23</t>
+          <t>-0,81; 0,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,34</t>
+          <t>0,29; 1,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,7</t>
+          <t>-0,7; 0,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,73</t>
+          <t>-0,35; 0,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,25</t>
+          <t>-0,57; 0,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,87</t>
+          <t>0,13; 1,01</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 24,56</t>
+          <t>-56,23; 25,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5,37; 153,14</t>
+          <t>13,15; 172,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 42,37</t>
+          <t>-30,94; 40,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 44,93</t>
+          <t>-14,77; 53,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 17,62</t>
+          <t>-32,86; 21,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,58; 63,52</t>
+          <t>7,54; 71,89</t>
         </is>
       </c>
     </row>
